--- a/seed_data/starrings.xlsx
+++ b/seed_data/starrings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/seed_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B091862-3614-401B-B5F8-C4F991E0159F}"/>
+  <xr:revisionPtr revIDLastSave="102" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CFE770C-7FF2-4DC1-9CCE-56C883378770}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Ava Canning</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Nazli Leetch</t>
   </si>
   <si>
-    <t>Beth Dimond</t>
-  </si>
-  <si>
     <t>Lauren Torpey</t>
   </si>
   <si>
@@ -96,12 +93,6 @@
     <t>Aisling O'Kelly</t>
   </si>
   <si>
-    <t>Anna Delany</t>
-  </si>
-  <si>
-    <t>Isabella McGrath</t>
-  </si>
-  <si>
     <t>Sophia Nulty</t>
   </si>
   <si>
@@ -144,31 +135,22 @@
     <t>Sriya Komati Reddy</t>
   </si>
   <si>
-    <t>Cathy Treneman</t>
-  </si>
-  <si>
     <t>Rachel Sparrow</t>
   </si>
   <si>
     <t>Lorraine Bagnall</t>
   </si>
   <si>
-    <t>Lavanya Rajesh</t>
-  </si>
-  <si>
     <t>Helen O'Kelly</t>
   </si>
   <si>
-    <t>Ruth McGonnell</t>
-  </si>
-  <si>
-    <t>Emily Bowe</t>
-  </si>
-  <si>
-    <t>Aisling Dunne</t>
-  </si>
-  <si>
-    <t>Caoimhe O'Brien</t>
+    <t>Lara di Nardi</t>
+  </si>
+  <si>
+    <t>Anna Payet</t>
+  </si>
+  <si>
+    <t>Lavanya Rajeshkanna</t>
   </si>
 </sst>
 </file>
@@ -486,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -526,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -535,13 +517,13 @@
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -549,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -558,44 +540,44 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -604,36 +586,36 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -644,55 +626,25 @@
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G16" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/seed_data/starrings.xlsx
+++ b/seed_data/starrings.xlsx
@@ -1,31 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/seed_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e2daab8ffa038972/Desktop/Fantasy Cricket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="11_F25DC773A252ABDACC104883891D63A25ADE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CFE770C-7FF2-4DC1-9CCE-56C883378770}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{387DE9DB-07CF-4049-826E-5FAF1F9EE2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="480" windowWidth="17280" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t>May2026</t>
+  </si>
+  <si>
+    <t>June2026</t>
+  </si>
   <si>
     <t>Ava Canning</t>
   </si>
@@ -51,6 +68,9 @@
     <t>Katie Dillon</t>
   </si>
   <si>
+    <t>Isabel Saeed-Maguire</t>
+  </si>
+  <si>
     <t>Orla Bagnall</t>
   </si>
   <si>
@@ -81,9 +101,18 @@
     <t>Olivia Pacitto</t>
   </si>
   <si>
+    <t>Katie Dagostino</t>
+  </si>
+  <si>
     <t>Nazli Leetch</t>
   </si>
   <si>
+    <t>Beth Dimond</t>
+  </si>
+  <si>
+    <t>Leah Mullett</t>
+  </si>
+  <si>
     <t>Lauren Torpey</t>
   </si>
   <si>
@@ -93,6 +122,12 @@
     <t>Aisling O'Kelly</t>
   </si>
   <si>
+    <t>Anna Delany</t>
+  </si>
+  <si>
+    <t>Isabella McGrath</t>
+  </si>
+  <si>
     <t>Sophia Nulty</t>
   </si>
   <si>
@@ -108,15 +143,6 @@
     <t>Zara Deacon</t>
   </si>
   <si>
-    <t>Isabel Saeed-Maguire</t>
-  </si>
-  <si>
-    <t>Katie Dagostino</t>
-  </si>
-  <si>
-    <t>Leah Mullett</t>
-  </si>
-  <si>
     <t>Daphne Deacon</t>
   </si>
   <si>
@@ -135,35 +161,80 @@
     <t>Sriya Komati Reddy</t>
   </si>
   <si>
+    <t>Cathy Treneman</t>
+  </si>
+  <si>
     <t>Rachel Sparrow</t>
   </si>
   <si>
     <t>Lorraine Bagnall</t>
   </si>
   <si>
+    <t>Lavanya Rajesh</t>
+  </si>
+  <si>
     <t>Helen O'Kelly</t>
   </si>
   <si>
+    <t>Ruth McGonnell</t>
+  </si>
+  <si>
+    <t>Emily Bowe</t>
+  </si>
+  <si>
+    <t>Aisling Dunne</t>
+  </si>
+  <si>
+    <t>Caoimhe O'Brien</t>
+  </si>
+  <si>
+    <t>Catherine Nulty</t>
+  </si>
+  <si>
+    <t>Georgina Mullett</t>
+  </si>
+  <si>
+    <t>Deivanai Alagappan</t>
+  </si>
+  <si>
     <t>Lara di Nardi</t>
   </si>
   <si>
+    <t>Maria Cryan</t>
+  </si>
+  <si>
+    <t>Rachel Kelly</t>
+  </si>
+  <si>
+    <t>Amanda Simoes</t>
+  </si>
+  <si>
+    <t>Stephanie Merenbach</t>
+  </si>
+  <si>
     <t>Anna Payet</t>
   </si>
   <si>
-    <t>Lavanya Rajeshkanna</t>
+    <t>Player</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,8 +257,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,183 +542,600 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B1">
-        <v>1.2</v>
-      </c>
-      <c r="C1">
-        <v>2.1</v>
-      </c>
-      <c r="D1">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E1">
-        <v>3.1</v>
-      </c>
-      <c r="F1">
-        <v>3.2</v>
-      </c>
-      <c r="G1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C5">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C6">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C7">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>1.2</v>
+      </c>
+      <c r="C8">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>1.2</v>
+      </c>
+      <c r="C9">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1.2</v>
+      </c>
+      <c r="C10">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1.2</v>
+      </c>
+      <c r="C11">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1.2</v>
+      </c>
+      <c r="C12">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>2.1</v>
+      </c>
+      <c r="C13">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>2.1</v>
+      </c>
+      <c r="C14">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>2.1</v>
+      </c>
+      <c r="C15">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>2.1</v>
+      </c>
+      <c r="C16">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>2.1</v>
+      </c>
+      <c r="C17">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>2.1</v>
+      </c>
+      <c r="C18">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C19">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C20">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C21">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C22">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>3.1</v>
+      </c>
+      <c r="C24">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25">
+        <v>3.1</v>
+      </c>
+      <c r="C25">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26">
+        <v>3.1</v>
+      </c>
+      <c r="C26">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="B27">
+        <v>3.1</v>
+      </c>
+      <c r="C27">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29">
+        <v>3.1</v>
+      </c>
+      <c r="C29">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31">
+        <v>3.2</v>
+      </c>
+      <c r="C31">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32">
+        <v>3.2</v>
+      </c>
+      <c r="C32">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33">
+        <v>3.2</v>
+      </c>
+      <c r="C33">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34">
+        <v>3.2</v>
+      </c>
+      <c r="C34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G8" t="s">
+      <c r="B36">
+        <v>4</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G9" t="s">
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G10" t="s">
-        <v>38</v>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>4</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>4</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>4</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58">
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
